--- a/csv/export-fundanet/scopus.xlsx
+++ b/csv/export-fundanet/scopus.xlsx
@@ -269,7 +269,7 @@
         <v>67</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>40</v>
